--- a/data/trans_orig/P11_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P11_R-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que el dolor dificultó su trabajo habitual las últimas 4 semanas en 2007</t>
+          <t>Población que el dolor dificultó su trabajo habitual las últimas 4 semanas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>313143</t>
+          <t>317123</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>374740</t>
+          <t>376700</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>582919</t>
+          <t>576774</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>650230</t>
+          <t>651438</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>916728</t>
+          <t>913881</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1010501</t>
+          <t>1010646</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>656983</t>
+          <t>655023</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>718580</t>
+          <t>714600</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>69,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>664883</t>
+          <t>663675</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>732194</t>
+          <t>738339</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,68%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1336334</t>
+          <t>1336189</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1430107</t>
+          <t>1432954</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>61,06%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>166573</t>
+          <t>170078</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>222703</t>
+          <t>220511</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>260896</t>
+          <t>263361</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>326576</t>
+          <t>323615</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>445760</t>
+          <t>444188</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>525093</t>
+          <t>526152</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,04%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1470710</t>
+          <t>1472902</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1526840</t>
+          <t>1523335</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1261097</t>
+          <t>1264058</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1326777</t>
+          <t>1324312</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2755993</t>
+          <t>2754934</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2835326</t>
+          <t>2836898</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,46%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43027</t>
+          <t>42080</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>73773</t>
+          <t>71801</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>64508</t>
+          <t>65154</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>98348</t>
+          <t>98085</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>114570</t>
+          <t>114685</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>160279</t>
+          <t>161209</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,68%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>477635</t>
+          <t>479607</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>508381</t>
+          <t>509328</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>378064</t>
+          <t>378327</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>411904</t>
+          <t>411258</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>867541</t>
+          <t>866611</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>913250</t>
+          <t>913135</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,84%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>552983</t>
+          <t>554337</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>642865</t>
+          <t>643076</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>931344</t>
+          <t>933971</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1036340</t>
+          <t>1042379</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1514374</t>
+          <t>1510899</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1655188</t>
+          <t>1649700</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,79%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2633678</t>
+          <t>2633467</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2723560</t>
+          <t>2722206</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2342857</t>
+          <t>2336818</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2447853</t>
+          <t>2445226</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5000553</t>
+          <t>5006041</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5141367</t>
+          <t>5144842</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>77,3%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que el dolor dificultó su trabajo habitual las últimas 4 semanas en 2012</t>
+          <t>Población que el dolor dificultó su trabajo habitual las últimas 4 semanas en 2012 (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>306127</t>
+          <t>306073</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>367644</t>
+          <t>368717</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>658530</t>
+          <t>658205</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>732015</t>
+          <t>737358</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>55,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>988573</t>
+          <t>979789</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1083215</t>
+          <t>1081268</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>46,86%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>602904</t>
+          <t>601831</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>664421</t>
+          <t>664475</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>604843</t>
+          <t>599500</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>678328</t>
+          <t>678653</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1224190</t>
+          <t>1226137</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1318832</t>
+          <t>1327616</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>57,54%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>221262</t>
+          <t>224103</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>286132</t>
+          <t>285262</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>330519</t>
+          <t>328332</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>398504</t>
+          <t>399302</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>568592</t>
+          <t>573574</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>662993</t>
+          <t>666500</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,97%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1666993</t>
+          <t>1667863</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1731863</t>
+          <t>1729022</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1356372</t>
+          <t>1355574</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1424357</t>
+          <t>1426544</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3045008</t>
+          <t>3041501</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3139409</t>
+          <t>3134427</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,53%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37003</t>
+          <t>38254</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>68307</t>
+          <t>68370</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38029</t>
+          <t>38718</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>66081</t>
+          <t>66521</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>83648</t>
+          <t>82553</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>125659</t>
+          <t>127079</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,55%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>410711</t>
+          <t>410648</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>442015</t>
+          <t>440764</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>392550</t>
+          <t>392110</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>420602</t>
+          <t>419913</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>811990</t>
+          <t>810570</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>854001</t>
+          <t>855096</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,2%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>593785</t>
+          <t>593790</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>684369</t>
+          <t>689994</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1053890</t>
+          <t>1052307</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1168678</t>
+          <t>1169965</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1674321</t>
+          <t>1684192</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1825749</t>
+          <t>1826680</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,27%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2718321</t>
+          <t>2712696</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2808905</t>
+          <t>2808900</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2381687</t>
+          <t>2380400</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2496475</t>
+          <t>2498058</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>67,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>70,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5127306</t>
+          <t>5126375</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5278734</t>
+          <t>5268863</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>75,78%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que el dolor dificultó su trabajo habitual las últimas 4 semanas en 2016</t>
+          <t>Población que el dolor dificultó su trabajo habitual las últimas 4 semanas en 2016 (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>231382</t>
+          <t>230568</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>280446</t>
+          <t>282786</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>489959</t>
+          <t>491775</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>552914</t>
+          <t>556801</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>50,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>735057</t>
+          <t>735603</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>820348</t>
+          <t>819183</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>47,26%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>469965</t>
+          <t>467625</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>519029</t>
+          <t>519843</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>62,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>69,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>429914</t>
+          <t>426027</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>492869</t>
+          <t>491053</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>912891</t>
+          <t>914056</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>998182</t>
+          <t>997636</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,59%</t>
+          <t>57,56%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>285121</t>
+          <t>283732</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>351411</t>
+          <t>351987</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>364197</t>
+          <t>370830</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>444095</t>
+          <t>444658</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>677152</t>
+          <t>677963</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>775971</t>
+          <t>780289</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,31%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1709841</t>
+          <t>1709265</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1776131</t>
+          <t>1777520</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>82,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1535334</t>
+          <t>1534771</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1615232</t>
+          <t>1608599</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3264710</t>
+          <t>3260392</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3363529</t>
+          <t>3362718</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>83,22%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38865</t>
+          <t>38940</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>69024</t>
+          <t>68507</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>70228</t>
+          <t>68951</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>105434</t>
+          <t>105350</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,47 +4675,47 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
+          <t>12,6%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>19,25%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>139669</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>117402</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>164385</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
           <t>12,83%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>19,26%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>139669</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>116467</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>164983</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>12,83%</t>
-        </is>
-      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,1%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>472210</t>
+          <t>472727</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>502369</t>
+          <t>502294</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>441856</t>
+          <t>441940</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>477062</t>
+          <t>478339</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,47 +4788,47 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
+          <t>87,4%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>895</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>948855</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>924139</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>971122</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
           <t>87,17%</t>
         </is>
       </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>895</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>948855</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>923541</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>972057</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>87,17%</t>
-        </is>
-      </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,21%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>575905</t>
+          <t>579602</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>671295</t>
+          <t>671264</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>961333</t>
+          <t>958740</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1070121</t>
+          <t>1066126</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1568432</t>
+          <t>1573886</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1708508</t>
+          <t>1713275</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,97%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2681602</t>
+          <t>2681633</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2776992</t>
+          <t>2773295</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2439426</t>
+          <t>2443421</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2548214</t>
+          <t>2550807</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>69,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,61%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5153936</t>
+          <t>5149169</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5294012</t>
+          <t>5288558</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>77,07%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que el dolor dificultó su trabajo habitual las últimas 4 semanas en 2023</t>
+          <t>Población que el dolor dificultó su trabajo habitual las últimas 4 semanas en 2023 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>206935</t>
+          <t>207172</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>248397</t>
+          <t>250666</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>463800</t>
+          <t>461875</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>504590</t>
+          <t>506404</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>61,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>67,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>683306</t>
+          <t>680426</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>744345</t>
+          <t>740654</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>58,4%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>266541</t>
+          <t>264272</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>308003</t>
+          <t>307766</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>248744</t>
+          <t>246930</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>289534</t>
+          <t>291459</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>523928</t>
+          <t>527619</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>584967</t>
+          <t>587847</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>41,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>46,35%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>368304</t>
+          <t>360362</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>587772</t>
+          <t>589434</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>644914</t>
+          <t>645026</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1211366</t>
+          <t>1195170</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1116824</t>
+          <t>1137344</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1785608</t>
+          <t>1823327</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>40,28%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1700908</t>
+          <t>1699246</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1920376</t>
+          <t>1928318</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1026024</t>
+          <t>1042220</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1592476</t>
+          <t>1592364</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2740462</t>
+          <t>2702743</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3409246</t>
+          <t>3388726</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>74,87%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>103192</t>
+          <t>102316</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>141946</t>
+          <t>143364</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>152550</t>
+          <t>151999</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>189930</t>
+          <t>192944</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>266668</t>
+          <t>263331</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>322548</t>
+          <t>318915</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,45%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>503262</t>
+          <t>501844</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>542016</t>
+          <t>542892</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>469242</t>
+          <t>466228</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>506622</t>
+          <t>507173</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>70,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>76,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>981832</t>
+          <t>985465</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1037712</t>
+          <t>1041049</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>79,81%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>673187</t>
+          <t>674185</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>950897</t>
+          <t>941163</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1310531</t>
+          <t>1308561</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1911746</t>
+          <t>1863316</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2084771</t>
+          <t>2098662</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2759438</t>
+          <t>2870540</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>40,44%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2497929</t>
+          <t>2507663</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2775639</t>
+          <t>2774641</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1738150</t>
+          <t>1786580</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2339365</t>
+          <t>2341335</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4339285</t>
+          <t>4228183</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5013952</t>
+          <t>5000061</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>70,44%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P11_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P11_R-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>317123</t>
+          <t>315469</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>376700</t>
+          <t>376737</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>576774</t>
+          <t>579791</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>651438</t>
+          <t>651888</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>44,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>49,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>913881</t>
+          <t>913538</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1010646</t>
+          <t>1008966</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>42,99%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>655023</t>
+          <t>654986</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>714600</t>
+          <t>716254</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>663675</t>
+          <t>663225</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>738339</t>
+          <t>735322</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>50,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,14%</t>
+          <t>55,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1336189</t>
+          <t>1337869</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1432954</t>
+          <t>1433297</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,94%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,06%</t>
+          <t>61,07%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>170078</t>
+          <t>168478</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>220511</t>
+          <t>219758</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>263361</t>
+          <t>259459</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>323615</t>
+          <t>323156</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>444188</t>
+          <t>446427</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>526152</t>
+          <t>531210</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,19%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1472902</t>
+          <t>1473655</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1523335</t>
+          <t>1524935</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1264058</t>
+          <t>1264517</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1324312</t>
+          <t>1328214</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2754934</t>
+          <t>2749876</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2836898</t>
+          <t>2834659</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,39%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42080</t>
+          <t>43270</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>71801</t>
+          <t>73137</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>65154</t>
+          <t>63959</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>98085</t>
+          <t>97846</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>114685</t>
+          <t>116546</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>161209</t>
+          <t>163273</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,89%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>479607</t>
+          <t>478271</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>509328</t>
+          <t>508138</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>378327</t>
+          <t>378566</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>411258</t>
+          <t>412453</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>866611</t>
+          <t>864547</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>913135</t>
+          <t>911274</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,66%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>554337</t>
+          <t>553244</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>643076</t>
+          <t>639974</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>933971</t>
+          <t>938814</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1042379</t>
+          <t>1044684</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1510899</t>
+          <t>1508456</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1649700</t>
+          <t>1648796</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,77%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2633467</t>
+          <t>2636569</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2722206</t>
+          <t>2723299</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2336818</t>
+          <t>2334513</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2445226</t>
+          <t>2440383</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5006041</t>
+          <t>5006945</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5144842</t>
+          <t>5147285</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>77,34%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>306073</t>
+          <t>303877</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>368717</t>
+          <t>365182</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>658205</t>
+          <t>659633</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>737358</t>
+          <t>733827</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,24%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>54,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>979789</t>
+          <t>982856</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1081268</t>
+          <t>1079660</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>46,79%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>601831</t>
+          <t>605366</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>664475</t>
+          <t>666671</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>68,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>599500</t>
+          <t>603031</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>678653</t>
+          <t>677225</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1226137</t>
+          <t>1227745</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1327616</t>
+          <t>1324549</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>57,4%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>224103</t>
+          <t>221750</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>285262</t>
+          <t>284820</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>328332</t>
+          <t>330691</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>399302</t>
+          <t>399499</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>573574</t>
+          <t>571528</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>666500</t>
+          <t>664068</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,91%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1667863</t>
+          <t>1668305</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1729022</t>
+          <t>1731375</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1355574</t>
+          <t>1355377</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1426544</t>
+          <t>1424185</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3041501</t>
+          <t>3043933</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3134427</t>
+          <t>3136473</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,59%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38254</t>
+          <t>37728</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>68370</t>
+          <t>67848</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38718</t>
+          <t>38469</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>66521</t>
+          <t>68160</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>82553</t>
+          <t>79777</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>127079</t>
+          <t>120805</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>12,88%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>410648</t>
+          <t>411170</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>440764</t>
+          <t>441290</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>392110</t>
+          <t>390471</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>419913</t>
+          <t>420162</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>810570</t>
+          <t>816844</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>855096</t>
+          <t>857872</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,49%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>593790</t>
+          <t>595864</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>689994</t>
+          <t>697148</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1052307</t>
+          <t>1048894</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1169965</t>
+          <t>1166102</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1684192</t>
+          <t>1680038</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1826680</t>
+          <t>1822091</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,21%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2712696</t>
+          <t>2705542</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2808900</t>
+          <t>2806826</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2380400</t>
+          <t>2384263</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2498058</t>
+          <t>2501471</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5126375</t>
+          <t>5130964</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5268863</t>
+          <t>5273017</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>75,84%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>230568</t>
+          <t>228619</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>282786</t>
+          <t>278909</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>491775</t>
+          <t>490056</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>556801</t>
+          <t>555086</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>735603</t>
+          <t>734906</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>819183</t>
+          <t>822231</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>47,44%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>467625</t>
+          <t>471502</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>519843</t>
+          <t>521792</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>62,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>69,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>426027</t>
+          <t>427742</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>491053</t>
+          <t>492772</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>914056</t>
+          <t>911008</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>997636</t>
+          <t>998333</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>52,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>57,6%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>283732</t>
+          <t>283511</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>351987</t>
+          <t>354071</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>370830</t>
+          <t>371270</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>444658</t>
+          <t>445230</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>677963</t>
+          <t>671111</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>780289</t>
+          <t>774764</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,17%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1709265</t>
+          <t>1707181</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1777520</t>
+          <t>1777741</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1534771</t>
+          <t>1534199</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1608599</t>
+          <t>1608159</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3260392</t>
+          <t>3265917</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3362718</t>
+          <t>3369570</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>83,39%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38940</t>
+          <t>39078</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>68507</t>
+          <t>69387</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>68951</t>
+          <t>70186</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>105350</t>
+          <t>105920</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>117402</t>
+          <t>117712</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>164385</t>
+          <t>167269</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,37%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>472727</t>
+          <t>471847</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>502294</t>
+          <t>502156</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>441940</t>
+          <t>441370</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>478339</t>
+          <t>477104</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>924139</t>
+          <t>921255</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>971122</t>
+          <t>970812</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,19%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>579602</t>
+          <t>576838</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>671264</t>
+          <t>671786</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>958740</t>
+          <t>958661</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1066126</t>
+          <t>1071440</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1573886</t>
+          <t>1557734</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1713275</t>
+          <t>1708725</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,9%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2681633</t>
+          <t>2681111</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2773295</t>
+          <t>2776059</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2443421</t>
+          <t>2438107</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2550807</t>
+          <t>2550886</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5149169</t>
+          <t>5153719</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5288558</t>
+          <t>5304710</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>77,3%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>227190</t>
+          <t>247972</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>207172</t>
+          <t>226865</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>250666</t>
+          <t>270314</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>483841</t>
+          <t>519275</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>461875</t>
+          <t>497474</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>506404</t>
+          <t>542706</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>63,35%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>60,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>66,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>711032</t>
+          <t>767248</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>680426</t>
+          <t>734110</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>740654</t>
+          <t>797208</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>54,88%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>57,02%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>287748</t>
+          <t>330557</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>264272</t>
+          <t>308215</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>307766</t>
+          <t>351664</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>57,14%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>53,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>60,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>269493</t>
+          <t>300360</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>246930</t>
+          <t>276929</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>291459</t>
+          <t>322161</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>557241</t>
+          <t>630917</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>527619</t>
+          <t>600957</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>587847</t>
+          <t>664055</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>47,49%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>753334</t>
+          <t>819635</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>753334</t>
+          <t>819635</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>753334</t>
+          <t>819635</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1268273</t>
+          <t>1398165</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1268273</t>
+          <t>1398165</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1268273</t>
+          <t>1398165</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>510446</t>
+          <t>551915</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>360362</t>
+          <t>508361</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>589434</t>
+          <t>596694</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>813076</t>
+          <t>669612</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>645026</t>
+          <t>633056</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1195170</t>
+          <t>709721</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1323521</t>
+          <t>1221527</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1137344</t>
+          <t>1166477</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1823327</t>
+          <t>1290232</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>29,33%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1778234</t>
+          <t>1676608</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1699246</t>
+          <t>1631829</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1928318</t>
+          <t>1720162</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1424314</t>
+          <t>1501314</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1042220</t>
+          <t>1461205</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1592364</t>
+          <t>1537870</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>67,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3202549</t>
+          <t>3177922</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2702743</t>
+          <t>3109217</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3388726</t>
+          <t>3232972</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>72,23%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>70,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>73,49%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2288680</t>
+          <t>2228523</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2288680</t>
+          <t>2228523</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2288680</t>
+          <t>2228523</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237390</t>
+          <t>2170926</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237390</t>
+          <t>2170926</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237390</t>
+          <t>2170926</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4526070</t>
+          <t>4399449</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4526070</t>
+          <t>4399449</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4526070</t>
+          <t>4399449</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>121592</t>
+          <t>132837</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>102316</t>
+          <t>111733</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>143364</t>
+          <t>154687</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>170402</t>
+          <t>192224</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>151999</t>
+          <t>171403</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>192944</t>
+          <t>213479</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>291994</t>
+          <t>325061</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>263331</t>
+          <t>298768</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>318915</t>
+          <t>356999</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,74%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>523616</t>
+          <t>577171</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>501844</t>
+          <t>555321</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>542892</t>
+          <t>598275</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>488770</t>
+          <t>541064</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>466228</t>
+          <t>519809</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>507173</t>
+          <t>561885</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>70,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1012386</t>
+          <t>1118235</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>985465</t>
+          <t>1086297</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1041049</t>
+          <t>1144528</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>75,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,3%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>645208</t>
+          <t>710008</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>645208</t>
+          <t>710008</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>645208</t>
+          <t>710008</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>659172</t>
+          <t>733288</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>659172</t>
+          <t>733288</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>659172</t>
+          <t>733288</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1304380</t>
+          <t>1443296</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1304380</t>
+          <t>1443296</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1304380</t>
+          <t>1443296</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>859229</t>
+          <t>932725</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>674185</t>
+          <t>878168</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>941163</t>
+          <t>989048</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1467319</t>
+          <t>1381111</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1308561</t>
+          <t>1332680</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1863316</t>
+          <t>1434760</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>38,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2326548</t>
+          <t>2313836</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2098662</t>
+          <t>2239439</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2870540</t>
+          <t>2390504</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>33,01%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2589597</t>
+          <t>2584336</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2507663</t>
+          <t>2528013</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2774641</t>
+          <t>2638893</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>71,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2182577</t>
+          <t>2342739</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1786580</t>
+          <t>2289090</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2341335</t>
+          <t>2391170</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,15%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>4772175</t>
+          <t>4927074</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4228183</t>
+          <t>4850406</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5000061</t>
+          <t>5001471</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>68,04%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>66,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>69,07%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3448826</t>
+          <t>3517061</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3448826</t>
+          <t>3517061</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3448826</t>
+          <t>3517061</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3649896</t>
+          <t>3723850</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3649896</t>
+          <t>3723850</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3649896</t>
+          <t>3723850</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7098723</t>
+          <t>7240910</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7098723</t>
+          <t>7240910</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7098723</t>
+          <t>7240910</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
